--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.170.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.170.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.170" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.170" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.170.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.170.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0170.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0170.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.170.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.170.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.170" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.170" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y61"/>
+  <dimension ref="A1:Y67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 7 â€” 8</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢t</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]163</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]163</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 163</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: 8</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]163</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -624,7 +628,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •t</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -645,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -656,12 +664,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58 â€” 59</t>
+          <t>L71: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L25: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 7â€”8</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •t</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -673,17 +681,21 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 8</t>
+          <t>L5: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L115: punctuation artifact: repeated periods :: Cf the Court ..</t>
+          <t>L36: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: to dissolve . . . - - - •</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 85</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -713,14 +725,10 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Appearance by Guardian . . - . â€¢</t>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Appearance by Guardian . . - . •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -732,11 +740,15 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: .9</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •t</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
-      <c r="Q4" s="1" t="inlineStr"/>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>L115: punctuation artifact: repeated periods :: Cf the Court ..</t>
+        </is>
+      </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr"/>
       <c r="T4" s="1" t="inlineStr"/>
@@ -754,12 +766,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -768,14 +780,10 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 07 â€” 108</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: to dissolve . . . - - - â€¢</t>
+          <t>L36: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: to dissolve . . . - - - •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -787,7 +795,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 31</t>
+          <t>L25: symbol-only separator/garbage line :: . 7—8</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -823,26 +831,22 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58 â€” 59</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Common Injunction . . â€¢ .</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Common Injunction . . • .</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L16: isolated marker/symbol line :: 8</t>
+          <t>L14: symbol-only separator/garbage line :: . 7 — 8</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L52: symbol-only separator/garbage line :: . 31</t>
+          <t>L48: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -878,26 +882,22 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 07 â€” 108</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 54â€”55</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 85</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L18: isolated marker/symbol line :: . 9</t>
+          <t>L16: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 54</t>
+          <t>L49: isolated marker/symbol line :: .9</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -936,19 +936,19 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -56â€”57</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L21: isolated marker/symbol line :: 31</t>
+          <t>L18: isolated marker/symbol line :: . 9</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 64</t>
+          <t>L51: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -987,19 +987,19 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 57â€”58</t>
+          <t>L126: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L22: isolated marker/symbol line :: 54</t>
+          <t>L21: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 54</t>
+          <t>L52: symbol-only separator/garbage line :: . 31</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1038,19 +1038,19 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58â€”59</t>
+          <t>L136: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L24: isolated marker/symbol line :: 31</t>
+          <t>L22: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 54</t>
+          <t>L56: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1089,19 +1089,19 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 85</t>
+          <t>L174: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: 64</t>
+          <t>L24: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: 64</t>
+          <t>L58: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1138,21 +1138,17 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Of the Master, (See Â« Masterâ€™s Office.")</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 54</t>
+          <t>L25: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 60</t>
+          <t>L60: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1179,7 +1175,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1189,21 +1185,17 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: 85</t>
+          <t>L27: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 63</t>
+          <t>L62: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1230,7 +1222,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1240,21 +1232,17 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L31: isolated marker/symbol line :: 54</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 58</t>
+          <t>L66: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1291,21 +1279,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L134: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 16â€”17</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 84</t>
+          <t>L30: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 61</t>
+          <t>L68: symbol-only separator/garbage line :: 54—55</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1342,21 +1326,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: 64</t>
+          <t>L31: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 62</t>
+          <t>L70: symbol-only separator/garbage line :: -56—57</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1393,21 +1373,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: MASTERâ€™S OFFICE.</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 84</t>
+          <t>L35: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 62</t>
+          <t>L72: symbol-only separator/garbage line :: 57—58</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1432,21 +1408,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L150: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 07â€”108</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L39: symbol-only separator/garbage line :: 5455</t>
+          <t>L36: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 62</t>
+          <t>L74: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1471,21 +1443,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L160: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ry 8â€”9</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 84</t>
+          <t>L38: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 85</t>
+          <t>L76: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1510,21 +1478,17 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L42: symbol-only separator/garbage line :: - 56-57</t>
+          <t>L39: symbol-only separator/garbage line :: 5455</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L94: symbol-only separator/garbage line :: .84</t>
+          <t>L78: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1554,12 +1518,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 85</t>
+          <t>L41: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 84</t>
+          <t>L80: symbol-only separator/garbage line :: 58—59</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1589,12 +1553,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L45: symbol-only separator/garbage line :: 57-58</t>
+          <t>L42: symbol-only separator/garbage line :: - 56-57</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L97: symbol-only separator/garbage line :: .84</t>
+          <t>L84: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1624,12 +1588,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 85</t>
+          <t>L44: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 85</t>
+          <t>L86: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1659,12 +1623,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: a</t>
+          <t>L45: symbol-only separator/garbage line :: 57-58</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 108</t>
+          <t>L88: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1694,12 +1658,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 60</t>
+          <t>L47: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L90: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1729,12 +1693,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 108</t>
+          <t>L48: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L128: symbol-only separator/garbage line :: . 107</t>
+          <t>L92: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1764,12 +1728,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 63</t>
+          <t>L49: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 7</t>
+          <t>L94: symbol-only separator/garbage line :: .84</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1799,12 +1763,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: 58</t>
+          <t>L51: isolated marker/symbol line :: 108</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L133: symbol-only separator/garbage line :: .14</t>
+          <t>L95: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1834,12 +1798,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 107</t>
+          <t>L52: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L97: symbol-only separator/garbage line :: .84</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1869,12 +1833,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 7</t>
+          <t>L54: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L152: isolated marker/symbol line :: 4</t>
+          <t>L99: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1904,12 +1868,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 61</t>
+          <t>L56: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L154: isolated marker/symbol line :: 9</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 85</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1939,12 +1903,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: 62</t>
+          <t>L57: symbol-only separator/garbage line :: 58 — 59</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L158: isolated marker/symbol line :: .8</t>
+          <t>L103: isolated marker/symbol line :: 108</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1974,12 +1938,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: 62</t>
+          <t>L61: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L159: isolated marker/symbol line :: 8</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2009,12 +1973,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 62</t>
+          <t>L62: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L164: symbol-only separator/garbage line :: .93</t>
+          <t>L126: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2044,12 +2008,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L64: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L166: isolated marker/symbol line :: 93</t>
+          <t>L128: symbol-only separator/garbage line :: . 107</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2079,10 +2043,14 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L72: symbol-only separator/garbage line :: . 14</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="inlineStr"/>
+          <t>L66: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L130: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2110,10 +2078,14 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L74: symbol-only separator/garbage line :: 16-17</t>
-        </is>
-      </c>
-      <c r="O37" s="1" t="inlineStr"/>
+          <t>L69: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>L133: symbol-only separator/garbage line :: .14</t>
+        </is>
+      </c>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
       <c r="R37" s="1" t="inlineStr"/>
@@ -2141,10 +2113,14 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 9</t>
-        </is>
-      </c>
-      <c r="O38" s="1" t="inlineStr"/>
+          <t>L71: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>L134: symbol-only separator/garbage line :: 16—17</t>
+        </is>
+      </c>
       <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
       <c r="R38" s="1" t="inlineStr"/>
@@ -2172,10 +2148,14 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 8</t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="inlineStr"/>
+          <t>L72: symbol-only separator/garbage line :: . 14</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>L136: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2203,10 +2183,14 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 8</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr"/>
+          <t>L74: symbol-only separator/garbage line :: 16-17</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>L150: symbol-only separator/garbage line :: 07—108</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2234,10 +2218,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 93</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L75: symbol-only separator/garbage line :: 07 — 108</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L152: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2265,10 +2253,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 93</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L78: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L154: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2296,10 +2288,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 2</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L82: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L158: isolated marker/symbol line :: .8</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2327,10 +2323,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: t</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L84: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L159: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2358,10 +2358,14 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 54</t>
-        </is>
-      </c>
-      <c r="O45" s="1" t="inlineStr"/>
+          <t>L89: isolated marker/symbol line :: 93</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>L164: symbol-only separator/garbage line :: .93</t>
+        </is>
+      </c>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr"/>
       <c r="R45" s="1" t="inlineStr"/>
@@ -2389,10 +2393,14 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: 64</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr"/>
+          <t>L92: isolated marker/symbol line :: 93</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>L166: isolated marker/symbol line :: 93</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
       <c r="R46" s="1" t="inlineStr"/>
@@ -2420,10 +2428,14 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 54</t>
-        </is>
-      </c>
-      <c r="O47" s="1" t="inlineStr"/>
+          <t>L95: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L174: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -2451,7 +2463,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: 54</t>
+          <t>L96: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2482,7 +2494,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: 64</t>
+          <t>L99: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2513,7 +2525,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L105: symbol-only separator/garbage line :: 5455</t>
+          <t>L100: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2544,7 +2556,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L106: symbol-only separator/garbage line :: - 56-57</t>
+          <t>L101: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2575,7 +2587,7 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L107: symbol-only separator/garbage line :: 57-58</t>
+          <t>L102: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -2606,7 +2618,7 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: 60</t>
+          <t>L104: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -2637,7 +2649,7 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: 63</t>
+          <t>L105: symbol-only separator/garbage line :: 5455</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -2668,7 +2680,7 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: 58</t>
+          <t>L106: symbol-only separator/garbage line :: - 56-57</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -2699,7 +2711,7 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L113: isolated marker/symbol line :: 61</t>
+          <t>L107: symbol-only separator/garbage line :: 57-58</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -2730,7 +2742,7 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L114: isolated marker/symbol line :: 62</t>
+          <t>L108: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -2761,7 +2773,7 @@
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: 62</t>
+          <t>L109: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -2792,7 +2804,7 @@
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 62</t>
+          <t>L110: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -2823,7 +2835,7 @@
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 8</t>
+          <t>L111: symbol-only separator/garbage line :: 58 — 59</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -2854,7 +2866,7 @@
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L119: isolated marker/symbol line :: 8</t>
+          <t>L113: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -2869,6 +2881,192 @@
       <c r="X61" s="1" t="inlineStr"/>
       <c r="Y61" s="1" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr"/>
+      <c r="B62" s="1" t="inlineStr"/>
+      <c r="C62" s="1" t="inlineStr"/>
+      <c r="D62" s="1" t="inlineStr"/>
+      <c r="E62" s="1" t="inlineStr"/>
+      <c r="F62" s="1" t="inlineStr"/>
+      <c r="G62" s="1" t="inlineStr"/>
+      <c r="H62" s="1" t="inlineStr"/>
+      <c r="I62" s="1" t="inlineStr"/>
+      <c r="J62" s="1" t="inlineStr"/>
+      <c r="K62" s="1" t="inlineStr"/>
+      <c r="L62" s="1" t="inlineStr"/>
+      <c r="M62" s="1" t="inlineStr"/>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>L114: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O62" s="1" t="inlineStr"/>
+      <c r="P62" s="1" t="inlineStr"/>
+      <c r="Q62" s="1" t="inlineStr"/>
+      <c r="R62" s="1" t="inlineStr"/>
+      <c r="S62" s="1" t="inlineStr"/>
+      <c r="T62" s="1" t="inlineStr"/>
+      <c r="U62" s="1" t="inlineStr"/>
+      <c r="V62" s="1" t="inlineStr"/>
+      <c r="W62" s="1" t="inlineStr"/>
+      <c r="X62" s="1" t="inlineStr"/>
+      <c r="Y62" s="1" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr"/>
+      <c r="B63" s="1" t="inlineStr"/>
+      <c r="C63" s="1" t="inlineStr"/>
+      <c r="D63" s="1" t="inlineStr"/>
+      <c r="E63" s="1" t="inlineStr"/>
+      <c r="F63" s="1" t="inlineStr"/>
+      <c r="G63" s="1" t="inlineStr"/>
+      <c r="H63" s="1" t="inlineStr"/>
+      <c r="I63" s="1" t="inlineStr"/>
+      <c r="J63" s="1" t="inlineStr"/>
+      <c r="K63" s="1" t="inlineStr"/>
+      <c r="L63" s="1" t="inlineStr"/>
+      <c r="M63" s="1" t="inlineStr"/>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t>L115: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O63" s="1" t="inlineStr"/>
+      <c r="P63" s="1" t="inlineStr"/>
+      <c r="Q63" s="1" t="inlineStr"/>
+      <c r="R63" s="1" t="inlineStr"/>
+      <c r="S63" s="1" t="inlineStr"/>
+      <c r="T63" s="1" t="inlineStr"/>
+      <c r="U63" s="1" t="inlineStr"/>
+      <c r="V63" s="1" t="inlineStr"/>
+      <c r="W63" s="1" t="inlineStr"/>
+      <c r="X63" s="1" t="inlineStr"/>
+      <c r="Y63" s="1" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr"/>
+      <c r="B64" s="1" t="inlineStr"/>
+      <c r="C64" s="1" t="inlineStr"/>
+      <c r="D64" s="1" t="inlineStr"/>
+      <c r="E64" s="1" t="inlineStr"/>
+      <c r="F64" s="1" t="inlineStr"/>
+      <c r="G64" s="1" t="inlineStr"/>
+      <c r="H64" s="1" t="inlineStr"/>
+      <c r="I64" s="1" t="inlineStr"/>
+      <c r="J64" s="1" t="inlineStr"/>
+      <c r="K64" s="1" t="inlineStr"/>
+      <c r="L64" s="1" t="inlineStr"/>
+      <c r="M64" s="1" t="inlineStr"/>
+      <c r="N64" s="1" t="inlineStr">
+        <is>
+          <t>L116: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O64" s="1" t="inlineStr"/>
+      <c r="P64" s="1" t="inlineStr"/>
+      <c r="Q64" s="1" t="inlineStr"/>
+      <c r="R64" s="1" t="inlineStr"/>
+      <c r="S64" s="1" t="inlineStr"/>
+      <c r="T64" s="1" t="inlineStr"/>
+      <c r="U64" s="1" t="inlineStr"/>
+      <c r="V64" s="1" t="inlineStr"/>
+      <c r="W64" s="1" t="inlineStr"/>
+      <c r="X64" s="1" t="inlineStr"/>
+      <c r="Y64" s="1" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr"/>
+      <c r="B65" s="1" t="inlineStr"/>
+      <c r="C65" s="1" t="inlineStr"/>
+      <c r="D65" s="1" t="inlineStr"/>
+      <c r="E65" s="1" t="inlineStr"/>
+      <c r="F65" s="1" t="inlineStr"/>
+      <c r="G65" s="1" t="inlineStr"/>
+      <c r="H65" s="1" t="inlineStr"/>
+      <c r="I65" s="1" t="inlineStr"/>
+      <c r="J65" s="1" t="inlineStr"/>
+      <c r="K65" s="1" t="inlineStr"/>
+      <c r="L65" s="1" t="inlineStr"/>
+      <c r="M65" s="1" t="inlineStr"/>
+      <c r="N65" s="1" t="inlineStr">
+        <is>
+          <t>L117: symbol-only separator/garbage line :: 07 — 108</t>
+        </is>
+      </c>
+      <c r="O65" s="1" t="inlineStr"/>
+      <c r="P65" s="1" t="inlineStr"/>
+      <c r="Q65" s="1" t="inlineStr"/>
+      <c r="R65" s="1" t="inlineStr"/>
+      <c r="S65" s="1" t="inlineStr"/>
+      <c r="T65" s="1" t="inlineStr"/>
+      <c r="U65" s="1" t="inlineStr"/>
+      <c r="V65" s="1" t="inlineStr"/>
+      <c r="W65" s="1" t="inlineStr"/>
+      <c r="X65" s="1" t="inlineStr"/>
+      <c r="Y65" s="1" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr"/>
+      <c r="B66" s="1" t="inlineStr"/>
+      <c r="C66" s="1" t="inlineStr"/>
+      <c r="D66" s="1" t="inlineStr"/>
+      <c r="E66" s="1" t="inlineStr"/>
+      <c r="F66" s="1" t="inlineStr"/>
+      <c r="G66" s="1" t="inlineStr"/>
+      <c r="H66" s="1" t="inlineStr"/>
+      <c r="I66" s="1" t="inlineStr"/>
+      <c r="J66" s="1" t="inlineStr"/>
+      <c r="K66" s="1" t="inlineStr"/>
+      <c r="L66" s="1" t="inlineStr"/>
+      <c r="M66" s="1" t="inlineStr"/>
+      <c r="N66" s="1" t="inlineStr">
+        <is>
+          <t>L118: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O66" s="1" t="inlineStr"/>
+      <c r="P66" s="1" t="inlineStr"/>
+      <c r="Q66" s="1" t="inlineStr"/>
+      <c r="R66" s="1" t="inlineStr"/>
+      <c r="S66" s="1" t="inlineStr"/>
+      <c r="T66" s="1" t="inlineStr"/>
+      <c r="U66" s="1" t="inlineStr"/>
+      <c r="V66" s="1" t="inlineStr"/>
+      <c r="W66" s="1" t="inlineStr"/>
+      <c r="X66" s="1" t="inlineStr"/>
+      <c r="Y66" s="1" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr"/>
+      <c r="B67" s="1" t="inlineStr"/>
+      <c r="C67" s="1" t="inlineStr"/>
+      <c r="D67" s="1" t="inlineStr"/>
+      <c r="E67" s="1" t="inlineStr"/>
+      <c r="F67" s="1" t="inlineStr"/>
+      <c r="G67" s="1" t="inlineStr"/>
+      <c r="H67" s="1" t="inlineStr"/>
+      <c r="I67" s="1" t="inlineStr"/>
+      <c r="J67" s="1" t="inlineStr"/>
+      <c r="K67" s="1" t="inlineStr"/>
+      <c r="L67" s="1" t="inlineStr"/>
+      <c r="M67" s="1" t="inlineStr"/>
+      <c r="N67" s="1" t="inlineStr">
+        <is>
+          <t>L119: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O67" s="1" t="inlineStr"/>
+      <c r="P67" s="1" t="inlineStr"/>
+      <c r="Q67" s="1" t="inlineStr"/>
+      <c r="R67" s="1" t="inlineStr"/>
+      <c r="S67" s="1" t="inlineStr"/>
+      <c r="T67" s="1" t="inlineStr"/>
+      <c r="U67" s="1" t="inlineStr"/>
+      <c r="V67" s="1" t="inlineStr"/>
+      <c r="W67" s="1" t="inlineStr"/>
+      <c r="X67" s="1" t="inlineStr"/>
+      <c r="Y67" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
